--- a/Assets/Excel/StageModifierSO.xlsx
+++ b/Assets/Excel/StageModifierSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36811239-C030-4DCD-A39F-AF644B51C4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4885EDA-3B12-4884-A79D-A694BB71077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="1740" windowWidth="18540" windowHeight="15410" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
+    <workbookView xWindow="4640" yWindow="870" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
   </bookViews>
   <sheets>
     <sheet name="DestinyEffects" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="81">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -267,14 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>valueModifiactionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Percentage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -316,6 +308,18 @@
   </si>
   <si>
     <t>destinyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>valueModificationType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -708,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -915,19 +919,19 @@
         <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -941,7 +945,7 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -992,7 +996,7 @@
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1015,7 +1019,7 @@
         <v>-20</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>43</v>
@@ -1242,7 +1246,7 @@
         <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19">
         <v>20</v>
@@ -1325,7 +1329,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
         <v>44</v>
@@ -1337,12 +1341,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05532CA7-F06E-4199-AF52-A751CE55BB11}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -1350,12 +1355,13 @@
     <col min="3" max="3" width="17.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1369,16 +1375,19 @@
         <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>9030001</v>
       </c>
@@ -1395,10 +1404,13 @@
         <v>29</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <v>-5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>9030002</v>
       </c>
@@ -1417,8 +1429,11 @@
       <c r="F3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>9030003</v>
       </c>
@@ -1435,10 +1450,13 @@
         <v>29</v>
       </c>
       <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>9030004</v>
       </c>
@@ -1457,8 +1475,11 @@
       <c r="F5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>9030005</v>
       </c>
@@ -1475,10 +1496,13 @@
         <v>29</v>
       </c>
       <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>9030006</v>
       </c>
@@ -1495,10 +1519,13 @@
         <v>29</v>
       </c>
       <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
         <v>-10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>9030007</v>
       </c>
@@ -1515,10 +1542,13 @@
         <v>29</v>
       </c>
       <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
         <v>-10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>9030008</v>
       </c>
@@ -1535,29 +1565,38 @@
         <v>29</v>
       </c>
       <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>9030009</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
       </c>
-      <c r="G10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>9030010</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" t="s">
-        <v>78</v>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/StageModifierSO.xlsx
+++ b/Assets/Excel/StageModifierSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4885EDA-3B12-4884-A79D-A694BB71077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2665EA5C-FECC-4811-A5BE-5984610BFD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4640" yWindow="870" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
+    <workbookView xWindow="5770" yWindow="3880" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
   </bookViews>
   <sheets>
     <sheet name="DestinyEffects" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="82">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -320,6 +320,10 @@
   </si>
   <si>
     <t>maxLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pointPerLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1347,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05532CA7-F06E-4199-AF52-A751CE55BB11}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -1355,13 +1359,14 @@
     <col min="3" max="3" width="17.9140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1383,11 +1388,14 @@
       <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>9030001</v>
       </c>
@@ -1409,8 +1417,11 @@
       <c r="G2">
         <v>-5</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>9030002</v>
       </c>
@@ -1432,8 +1443,11 @@
       <c r="G3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>9030003</v>
       </c>
@@ -1455,8 +1469,11 @@
       <c r="G4">
         <v>-5</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>9030004</v>
       </c>
@@ -1478,8 +1495,11 @@
       <c r="G5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>9030005</v>
       </c>
@@ -1501,8 +1521,11 @@
       <c r="G6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>9030006</v>
       </c>
@@ -1524,8 +1547,11 @@
       <c r="G7">
         <v>-10</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>9030007</v>
       </c>
@@ -1547,8 +1573,11 @@
       <c r="G8">
         <v>-10</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>9030008</v>
       </c>
@@ -1570,8 +1599,11 @@
       <c r="G9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>9030009</v>
       </c>
@@ -1581,11 +1613,14 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>9030010</v>
       </c>
@@ -1595,12 +1630,16 @@
       <c r="F11">
         <v>3</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excel/StageModifierSO.xlsx
+++ b/Assets/Excel/StageModifierSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2665EA5C-FECC-4811-A5BE-5984610BFD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BEEAB-9312-4001-8F85-AF44343129A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5770" yWindow="3880" windowWidth="18540" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
+    <workbookView xWindow="8210" yWindow="800" windowWidth="15420" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
   </bookViews>
   <sheets>
     <sheet name="DestinyEffects" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="95">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -324,6 +324,58 @@
   </si>
   <si>
     <t>pointPerLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconSpritePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/Fortune_alliance_discount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/Fortune_chivalry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/Fortune_cost_reduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/Fortune_four_leaf_clover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/Fortune_hero_timer_advantage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_endless_rain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_hero_weakened</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_alliance_penalty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_cost_increase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_low_morale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_power_struggle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -697,18 +749,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7111E21D-E37F-41DF-B90C-E11D7A3BF0D3}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="81" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.58203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,8 +773,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>9010001</v>
       </c>
@@ -735,8 +790,11 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>9010002</v>
       </c>
@@ -749,8 +807,11 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>9010003</v>
       </c>
@@ -763,8 +824,11 @@
       <c r="D4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>9010004</v>
       </c>
@@ -777,8 +841,11 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>9010005</v>
       </c>
@@ -791,8 +858,11 @@
       <c r="D6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>9020001</v>
       </c>
@@ -805,8 +875,11 @@
       <c r="D7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>9020002</v>
       </c>
@@ -819,8 +892,11 @@
       <c r="D8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>9020003</v>
       </c>
@@ -833,8 +909,11 @@
       <c r="D9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>9020004</v>
       </c>
@@ -847,8 +926,11 @@
       <c r="D10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>9020005</v>
       </c>
@@ -861,8 +943,11 @@
       <c r="D11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>9020006</v>
       </c>
@@ -875,8 +960,11 @@
       <c r="D12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>9020007</v>
       </c>
@@ -888,6 +976,9 @@
       </c>
       <c r="D13" t="s">
         <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/StageModifierSO.xlsx
+++ b/Assets/Excel/StageModifierSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whals\OneDrive\Desktop\workspace\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BEEAB-9312-4001-8F85-AF44343129A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD382CD-7A2A-45D5-863F-2C9B3912E99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8210" yWindow="800" windowWidth="15420" windowHeight="15410" activeTab="2" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
+    <workbookView xWindow="10550" yWindow="540" windowWidth="15420" windowHeight="15410" xr2:uid="{EFCB9097-03F9-4FEA-8889-6DF9B346DC94}"/>
   </bookViews>
   <sheets>
     <sheet name="DestinyEffects" sheetId="1" r:id="rId1"/>
@@ -331,10 +331,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Destiny_Images/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Destiny_Images/Fortune_alliance_discount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -376,6 +372,10 @@
   </si>
   <si>
     <t>Destiny_Images/MIsfortune_power_struggle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny_Images/MIsfortune_low_manpower</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -791,7 +791,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -808,7 +808,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -825,7 +825,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -842,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -859,7 +859,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -876,7 +876,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -893,7 +893,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -910,7 +910,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -927,7 +927,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -944,7 +944,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -961,7 +961,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -978,7 +978,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
